--- a/result/morris/morris_first_inf_ONLY_Signed_N256_seed123.xlsx
+++ b/result/morris/morris_first_inf_ONLY_Signed_N256_seed123.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,33 +453,33 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>infection__infection_condition</t>
+          <t>zoospore_alive__vpd</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31.67805989583333</v>
+        <v>-21.74414062499999</v>
       </c>
       <c r="C2" t="n">
-        <v>32.55891927083333</v>
+        <v>26.59375</v>
       </c>
       <c r="D2" t="n">
-        <v>24.35323496077947</v>
+        <v>25.80726708746292</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>zoospore_alive__vpd</t>
+          <t>infection__infection_condition</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-26.89572482638888</v>
+        <v>19.32291666666667</v>
       </c>
       <c r="C3" t="n">
-        <v>28.90288628472221</v>
+        <v>22.9453125</v>
       </c>
       <c r="D3" t="n">
-        <v>29.84955932490239</v>
+        <v>22.32323881168077</v>
       </c>
     </row>
     <row r="4">
@@ -489,61 +489,61 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20.15082465277778</v>
+        <v>11.68760850694445</v>
       </c>
       <c r="C4" t="n">
-        <v>22.7400173611111</v>
+        <v>20.01790364583334</v>
       </c>
       <c r="D4" t="n">
-        <v>30.88424052883236</v>
+        <v>27.93908109023684</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mp_tmp__rh_wet_night</t>
+          <t>thresholds__min_spores</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16.76041666666667</v>
+        <v>9.963758680555559</v>
       </c>
       <c r="C5" t="n">
-        <v>21.88324652777778</v>
+        <v>18.37239583333333</v>
       </c>
       <c r="D5" t="n">
-        <v>26.54106837217525</v>
+        <v>24.66295251596151</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>sporulation__Tmax</t>
+          <t>mp_tmp__rh_wet_night</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.4998914930555556</v>
+        <v>8.541883680555561</v>
       </c>
       <c r="C6" t="n">
-        <v>6.316948784722221</v>
+        <v>10.63129340277778</v>
       </c>
       <c r="D6" t="n">
-        <v>13.81905635982969</v>
+        <v>14.57934139620193</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>sporulation__MP_min</t>
+          <t>sporulation__Tmax</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.125759548611112</v>
+        <v>-2.028754340277779</v>
       </c>
       <c r="C7" t="n">
-        <v>4.550021701388887</v>
+        <v>10.5363498263889</v>
       </c>
       <c r="D7" t="n">
-        <v>9.704248840573555</v>
+        <v>17.68378959836975</v>
       </c>
     </row>
     <row r="8">
@@ -553,93 +553,109 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.409613715277778</v>
+        <v>-1.605902777777778</v>
       </c>
       <c r="C8" t="n">
-        <v>3.048502604166667</v>
+        <v>7.639105902777781</v>
       </c>
       <c r="D8" t="n">
-        <v>8.953546583204657</v>
+        <v>15.68152224105359</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>incubation__spl_end</t>
+          <t>sporulation__Topt</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.77593315972222</v>
+        <v>-0.3309461805555557</v>
       </c>
       <c r="C9" t="n">
-        <v>2.77593315972222</v>
+        <v>5.241753472222223</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3843725891113952</v>
+        <v>12.37330297744212</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>deposition__rain_min</t>
+          <t>sporulation__Tmin</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.457682291666667</v>
+        <v>-0.9042968749999999</v>
       </c>
       <c r="C10" t="n">
-        <v>2.457682291666667</v>
+        <v>3.721354166666669</v>
       </c>
       <c r="D10" t="n">
-        <v>8.089148994510042</v>
+        <v>10.56644422251637</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>zoospore_alive__rain</t>
+          <t>incubation__spl_end</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.660698784722222</v>
+        <v>2.798177083333336</v>
       </c>
       <c r="C11" t="n">
-        <v>2.153103298611111</v>
+        <v>2.798177083333336</v>
       </c>
       <c r="D11" t="n">
-        <v>5.706706120504653</v>
+        <v>0.354433557433826</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>sporulation__Topt</t>
+          <t>zoospore_alive__rain</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.3836805555555555</v>
+        <v>0.7192925347222222</v>
       </c>
       <c r="C12" t="n">
-        <v>1.995659722222222</v>
+        <v>1.974066840277777</v>
       </c>
       <c r="D12" t="n">
-        <v>8.082384704273071</v>
+        <v>6.765947422061915</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>sporulation__Tmin</t>
+          <t>deposition__rain_min</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5784505208333334</v>
+        <v>1.640299479166666</v>
       </c>
       <c r="C13" t="n">
-        <v>0.865993923611111</v>
+        <v>1.953016493055555</v>
       </c>
       <c r="D13" t="n">
-        <v>6.137454876883607</v>
+        <v>6.362094600038708</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>sporulation__MP_min</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.5898437499999997</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1.853298611111111</v>
+      </c>
+      <c r="D14" t="n">
+        <v>5.995204030506802</v>
       </c>
     </row>
   </sheetData>
